--- a/tools/MiniTemplate/Datas/__beans__.xlsx
+++ b/tools/MiniTemplate/Datas/__beans__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dd\ET\tools\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D48972-29BF-48F3-9295-AF338A65EE97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{082FE57C-388E-437B-81AE-3830EC48B8B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -803,9 +803,6 @@
     <t>Skill.AttackMode</t>
   </si>
   <si>
-    <t>Drop.RewardType</t>
-  </si>
-  <si>
     <t>Gift.specialRewardType</t>
   </si>
   <si>
@@ -1053,6 +1050,10 @@
   </si>
   <si>
     <t>弹幕图标路径</t>
+  </si>
+  <si>
+    <t>DropEnum.RewardType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1153,11 +1154,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1440,7 +1441,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="42.265625" customWidth="1"/>
-    <col min="3" max="3" width="27.33203125" customWidth="1"/>
+    <col min="3" max="3" width="32.1328125" customWidth="1"/>
     <col min="4" max="4" width="21.73046875" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="34" customWidth="1"/>
@@ -1479,15 +1480,15 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
@@ -1731,7 +1732,7 @@
         <v>235</v>
       </c>
       <c r="N14" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.4">
@@ -1742,7 +1743,7 @@
         <v>235</v>
       </c>
       <c r="N15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.4">
@@ -1762,7 +1763,7 @@
         <v>237</v>
       </c>
       <c r="N16" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.4">
@@ -1773,7 +1774,7 @@
         <v>235</v>
       </c>
       <c r="N17" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.4">
@@ -1784,7 +1785,7 @@
         <v>235</v>
       </c>
       <c r="N18" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.4">
@@ -1804,7 +1805,7 @@
         <v>235</v>
       </c>
       <c r="N19" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.4">
@@ -1815,7 +1816,7 @@
         <v>235</v>
       </c>
       <c r="N20" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.4">
@@ -1849,7 +1850,7 @@
         <v>235</v>
       </c>
       <c r="N22" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.4">
@@ -1860,7 +1861,7 @@
         <v>235</v>
       </c>
       <c r="N23" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.4">
@@ -1871,7 +1872,7 @@
         <v>235</v>
       </c>
       <c r="N24" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.4">
@@ -1882,7 +1883,7 @@
         <v>235</v>
       </c>
       <c r="N25" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.4">
@@ -1893,7 +1894,7 @@
         <v>238</v>
       </c>
       <c r="N26" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.4">
@@ -1916,7 +1917,7 @@
         <v>235</v>
       </c>
       <c r="N27" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.4">
@@ -1944,7 +1945,7 @@
         <v>239</v>
       </c>
       <c r="N29" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.4">
@@ -1955,7 +1956,7 @@
         <v>240</v>
       </c>
       <c r="N30" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.4">
@@ -1966,7 +1967,7 @@
         <v>241</v>
       </c>
       <c r="N31" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.4">
@@ -1977,7 +1978,7 @@
         <v>241</v>
       </c>
       <c r="N32" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.4">
@@ -1988,7 +1989,7 @@
         <v>241</v>
       </c>
       <c r="N33" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.4">
@@ -2005,7 +2006,7 @@
         <v>238</v>
       </c>
       <c r="N34" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="35" spans="2:14" x14ac:dyDescent="0.4">
@@ -2016,7 +2017,7 @@
         <v>242</v>
       </c>
       <c r="N35" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.4">
@@ -2027,7 +2028,7 @@
         <v>243</v>
       </c>
       <c r="N36" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.4">
@@ -2038,7 +2039,7 @@
         <v>244</v>
       </c>
       <c r="N37" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.4">
@@ -2049,7 +2050,7 @@
         <v>235</v>
       </c>
       <c r="N38" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.4">
@@ -2060,7 +2061,7 @@
         <v>238</v>
       </c>
       <c r="N39" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.4">
@@ -2111,7 +2112,7 @@
         <v>245</v>
       </c>
       <c r="N42" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.4">
@@ -2122,7 +2123,7 @@
         <v>246</v>
       </c>
       <c r="N43" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.4">
@@ -2133,7 +2134,7 @@
         <v>247</v>
       </c>
       <c r="N44" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.4">
@@ -2144,7 +2145,7 @@
         <v>248</v>
       </c>
       <c r="N45" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.4">
@@ -2155,7 +2156,7 @@
         <v>248</v>
       </c>
       <c r="N46" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.4">
@@ -2175,7 +2176,7 @@
         <v>235</v>
       </c>
       <c r="N47" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.4">
@@ -2186,7 +2187,7 @@
         <v>238</v>
       </c>
       <c r="N48" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.4">
@@ -2197,7 +2198,7 @@
         <v>249</v>
       </c>
       <c r="N49" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="50" spans="2:14" x14ac:dyDescent="0.4">
@@ -2217,7 +2218,7 @@
         <v>245</v>
       </c>
       <c r="N50" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.4">
@@ -2240,7 +2241,7 @@
         <v>247</v>
       </c>
       <c r="N51" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="52" spans="2:14" x14ac:dyDescent="0.4">
@@ -2251,7 +2252,7 @@
         <v>248</v>
       </c>
       <c r="N52" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="53" spans="2:14" x14ac:dyDescent="0.4">
@@ -2262,7 +2263,7 @@
         <v>248</v>
       </c>
       <c r="N53" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="54" spans="2:14" x14ac:dyDescent="0.4">
@@ -2285,7 +2286,7 @@
         <v>247</v>
       </c>
       <c r="N54" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="55" spans="2:14" x14ac:dyDescent="0.4">
@@ -2296,7 +2297,7 @@
         <v>248</v>
       </c>
       <c r="N55" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="56" spans="2:14" x14ac:dyDescent="0.4">
@@ -2307,7 +2308,7 @@
         <v>248</v>
       </c>
       <c r="N56" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="57" spans="2:14" x14ac:dyDescent="0.4">
@@ -2330,7 +2331,7 @@
         <v>243</v>
       </c>
       <c r="N57" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="58" spans="2:14" x14ac:dyDescent="0.4">
@@ -2353,7 +2354,7 @@
         <v>250</v>
       </c>
       <c r="N58" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="59" spans="2:14" x14ac:dyDescent="0.4">
@@ -2364,7 +2365,7 @@
         <v>250</v>
       </c>
       <c r="N59" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="60" spans="2:14" x14ac:dyDescent="0.4">
@@ -2387,7 +2388,7 @@
         <v>251</v>
       </c>
       <c r="N60" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="61" spans="2:14" x14ac:dyDescent="0.4">
@@ -2398,7 +2399,7 @@
         <v>251</v>
       </c>
       <c r="N61" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="62" spans="2:14" x14ac:dyDescent="0.4">
@@ -2421,7 +2422,7 @@
         <v>248</v>
       </c>
       <c r="N62" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="63" spans="2:14" x14ac:dyDescent="0.4">
@@ -2432,7 +2433,7 @@
         <v>248</v>
       </c>
       <c r="N63" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="64" spans="2:14" x14ac:dyDescent="0.4">
@@ -2443,7 +2444,7 @@
         <v>248</v>
       </c>
       <c r="N64" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="65" spans="2:14" x14ac:dyDescent="0.4">
@@ -2466,7 +2467,7 @@
         <v>248</v>
       </c>
       <c r="N65" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.4">
@@ -2477,7 +2478,7 @@
         <v>248</v>
       </c>
       <c r="N66" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="67" spans="2:14" x14ac:dyDescent="0.4">
@@ -2488,7 +2489,7 @@
         <v>248</v>
       </c>
       <c r="N67" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="68" spans="2:14" x14ac:dyDescent="0.4">
@@ -2499,7 +2500,7 @@
         <v>248</v>
       </c>
       <c r="N68" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="69" spans="2:14" x14ac:dyDescent="0.4">
@@ -2522,7 +2523,7 @@
         <v>247</v>
       </c>
       <c r="N69" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="70" spans="2:14" x14ac:dyDescent="0.4">
@@ -2533,7 +2534,7 @@
         <v>248</v>
       </c>
       <c r="N70" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="71" spans="2:14" x14ac:dyDescent="0.4">
@@ -2544,7 +2545,7 @@
         <v>248</v>
       </c>
       <c r="N71" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="72" spans="2:14" x14ac:dyDescent="0.4">
@@ -2567,7 +2568,7 @@
         <v>252</v>
       </c>
       <c r="N72" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="73" spans="2:14" x14ac:dyDescent="0.4">
@@ -2578,7 +2579,7 @@
         <v>247</v>
       </c>
       <c r="N73" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="74" spans="2:14" x14ac:dyDescent="0.4">
@@ -2589,7 +2590,7 @@
         <v>248</v>
       </c>
       <c r="N74" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="75" spans="2:14" x14ac:dyDescent="0.4">
@@ -2600,7 +2601,7 @@
         <v>248</v>
       </c>
       <c r="N75" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="76" spans="2:14" x14ac:dyDescent="0.4">
@@ -2623,7 +2624,7 @@
         <v>252</v>
       </c>
       <c r="N76" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="77" spans="2:14" x14ac:dyDescent="0.4">
@@ -2634,7 +2635,7 @@
         <v>240</v>
       </c>
       <c r="N77" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="78" spans="2:14" x14ac:dyDescent="0.4">
@@ -2645,7 +2646,7 @@
         <v>248</v>
       </c>
       <c r="N78" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="79" spans="2:14" x14ac:dyDescent="0.4">
@@ -2656,7 +2657,7 @@
         <v>248</v>
       </c>
       <c r="N79" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="80" spans="2:14" x14ac:dyDescent="0.4">
@@ -2679,7 +2680,7 @@
         <v>248</v>
       </c>
       <c r="N80" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="81" spans="2:14" x14ac:dyDescent="0.4">
@@ -2702,7 +2703,7 @@
         <v>248</v>
       </c>
       <c r="N81" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="82" spans="2:14" x14ac:dyDescent="0.4">
@@ -2725,7 +2726,7 @@
         <v>235</v>
       </c>
       <c r="N82" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="83" spans="2:14" x14ac:dyDescent="0.4">
@@ -2736,7 +2737,7 @@
         <v>235</v>
       </c>
       <c r="N83" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="84" spans="2:14" x14ac:dyDescent="0.4">
@@ -2759,7 +2760,7 @@
         <v>253</v>
       </c>
       <c r="N84" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="85" spans="2:14" x14ac:dyDescent="0.4">
@@ -2770,7 +2771,7 @@
         <v>248</v>
       </c>
       <c r="N85" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="86" spans="2:14" x14ac:dyDescent="0.4">
@@ -2781,7 +2782,7 @@
         <v>248</v>
       </c>
       <c r="N86" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="87" spans="2:14" x14ac:dyDescent="0.4">
@@ -2804,7 +2805,7 @@
         <v>245</v>
       </c>
       <c r="N87" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="88" spans="2:14" x14ac:dyDescent="0.4">
@@ -2815,7 +2816,7 @@
         <v>254</v>
       </c>
       <c r="N88" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="89" spans="2:14" x14ac:dyDescent="0.4">
@@ -2838,7 +2839,7 @@
         <v>255</v>
       </c>
       <c r="N89" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="90" spans="2:14" x14ac:dyDescent="0.4">
@@ -2861,7 +2862,7 @@
         <v>235</v>
       </c>
       <c r="N90" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="91" spans="2:14" x14ac:dyDescent="0.4">
@@ -2884,7 +2885,7 @@
         <v>235</v>
       </c>
       <c r="N91" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="92" spans="2:14" x14ac:dyDescent="0.4">
@@ -2907,7 +2908,7 @@
         <v>235</v>
       </c>
       <c r="N92" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="93" spans="2:14" x14ac:dyDescent="0.4">
@@ -2930,7 +2931,7 @@
         <v>254</v>
       </c>
       <c r="N93" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="94" spans="2:14" x14ac:dyDescent="0.4">
@@ -2967,7 +2968,7 @@
         <v>256</v>
       </c>
       <c r="N95" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="96" spans="2:14" x14ac:dyDescent="0.4">
@@ -2978,7 +2979,7 @@
         <v>238</v>
       </c>
       <c r="N96" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="97" spans="2:14" x14ac:dyDescent="0.4">
@@ -3001,7 +3002,7 @@
         <v>238</v>
       </c>
       <c r="N97" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="98" spans="2:14" x14ac:dyDescent="0.4">
@@ -3024,7 +3025,7 @@
         <v>246</v>
       </c>
       <c r="N98" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="99" spans="2:14" x14ac:dyDescent="0.4">
@@ -3035,7 +3036,7 @@
         <v>235</v>
       </c>
       <c r="N99" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="100" spans="2:14" x14ac:dyDescent="0.4">
@@ -3058,7 +3059,7 @@
         <v>257</v>
       </c>
       <c r="N100" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="101" spans="2:14" x14ac:dyDescent="0.4">
@@ -3069,7 +3070,7 @@
         <v>235</v>
       </c>
       <c r="N101" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="102" spans="2:14" x14ac:dyDescent="0.4">
@@ -3092,7 +3093,7 @@
         <v>258</v>
       </c>
       <c r="N102" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="103" spans="2:14" x14ac:dyDescent="0.4">
@@ -3103,7 +3104,7 @@
         <v>235</v>
       </c>
       <c r="N103" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="104" spans="2:14" x14ac:dyDescent="0.4">
@@ -3126,7 +3127,7 @@
         <v>235</v>
       </c>
       <c r="N104" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="105" spans="2:14" x14ac:dyDescent="0.4">
@@ -3149,7 +3150,7 @@
         <v>243</v>
       </c>
       <c r="N105" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="106" spans="2:14" x14ac:dyDescent="0.4">
@@ -3172,7 +3173,7 @@
         <v>242</v>
       </c>
       <c r="N106" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="107" spans="2:14" x14ac:dyDescent="0.4">
@@ -3195,25 +3196,25 @@
         <v>239</v>
       </c>
       <c r="N107" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="108" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B108" s="4" t="s">
+      <c r="B108" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C108" s="4"/>
-      <c r="D108" s="4"/>
-      <c r="E108" s="4" t="s">
+      <c r="C108" s="3"/>
+      <c r="D108" s="3"/>
+      <c r="E108" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="F108" s="4" t="s">
+      <c r="F108" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="J108" s="4"/>
-      <c r="L108" s="4"/>
-      <c r="M108" s="4"/>
-      <c r="N108" s="4"/>
+      <c r="J108" s="3"/>
+      <c r="L108" s="3"/>
+      <c r="M108" s="3"/>
+      <c r="N108" s="3"/>
     </row>
     <row r="109" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B109" t="s">
@@ -3291,7 +3292,7 @@
         <v>27</v>
       </c>
       <c r="N113" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="114" spans="2:14" x14ac:dyDescent="0.4">
@@ -3314,7 +3315,7 @@
         <v>235</v>
       </c>
       <c r="N114" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="115" spans="2:14" x14ac:dyDescent="0.4">
@@ -3325,25 +3326,25 @@
         <v>235</v>
       </c>
       <c r="N115" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="116" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B116" s="4" t="s">
+      <c r="B116" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C116" s="4"/>
-      <c r="D116" s="4"/>
-      <c r="E116" s="4" t="s">
+      <c r="C116" s="3"/>
+      <c r="D116" s="3"/>
+      <c r="E116" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="F116" s="4" t="s">
+      <c r="F116" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="J116" s="4"/>
-      <c r="L116" s="4"/>
-      <c r="M116" s="4"/>
-      <c r="N116" s="4"/>
+      <c r="J116" s="3"/>
+      <c r="L116" s="3"/>
+      <c r="M116" s="3"/>
+      <c r="N116" s="3"/>
     </row>
     <row r="117" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B117" t="s">
@@ -3379,26 +3380,26 @@
       </c>
     </row>
     <row r="120" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B120" s="4" t="s">
+      <c r="B120" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C120" s="4"/>
-      <c r="D120" s="4"/>
-      <c r="E120" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F120" s="4" t="s">
+      <c r="C120" s="3"/>
+      <c r="D120" s="3"/>
+      <c r="E120" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F120" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="J120" s="4" t="s">
+      <c r="J120" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="L120" s="4" t="s">
+      <c r="L120" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="M120" s="4"/>
-      <c r="N120" s="4" t="s">
-        <v>326</v>
+      <c r="M120" s="3"/>
+      <c r="N120" s="3" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="121" spans="2:14" x14ac:dyDescent="0.4">
@@ -3409,7 +3410,7 @@
         <v>235</v>
       </c>
       <c r="N121" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="122" spans="2:14" x14ac:dyDescent="0.4">
@@ -3420,7 +3421,7 @@
         <v>248</v>
       </c>
       <c r="N122" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="123" spans="2:14" x14ac:dyDescent="0.4">
@@ -3440,7 +3441,7 @@
         <v>235</v>
       </c>
       <c r="N123" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="124" spans="2:14" x14ac:dyDescent="0.4">
@@ -3451,7 +3452,7 @@
         <v>235</v>
       </c>
       <c r="N124" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="125" spans="2:14" x14ac:dyDescent="0.4">
@@ -3462,7 +3463,7 @@
         <v>235</v>
       </c>
       <c r="N125" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="126" spans="2:14" x14ac:dyDescent="0.4">
@@ -3482,7 +3483,7 @@
         <v>235</v>
       </c>
       <c r="N126" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="127" spans="2:14" x14ac:dyDescent="0.4">
@@ -3493,7 +3494,7 @@
         <v>235</v>
       </c>
       <c r="N127" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="128" spans="2:14" x14ac:dyDescent="0.4">
@@ -3504,7 +3505,7 @@
         <v>235</v>
       </c>
       <c r="N128" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="129" spans="2:14" x14ac:dyDescent="0.4">
@@ -3515,7 +3516,7 @@
         <v>235</v>
       </c>
       <c r="N129" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="130" spans="2:14" x14ac:dyDescent="0.4">
@@ -3531,11 +3532,11 @@
       <c r="J130" t="s">
         <v>230</v>
       </c>
-      <c r="L130" t="s">
-        <v>259</v>
+      <c r="L130" s="2" t="s">
+        <v>342</v>
       </c>
       <c r="N130" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="131" spans="2:14" x14ac:dyDescent="0.4">
@@ -3546,7 +3547,7 @@
         <v>235</v>
       </c>
       <c r="N131" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="132" spans="2:14" x14ac:dyDescent="0.4">
@@ -3557,7 +3558,7 @@
         <v>235</v>
       </c>
       <c r="N132" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="133" spans="2:14" x14ac:dyDescent="0.4">
@@ -3568,7 +3569,7 @@
         <v>235</v>
       </c>
       <c r="N133" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="134" spans="2:14" x14ac:dyDescent="0.4">
@@ -3585,10 +3586,10 @@
         <v>230</v>
       </c>
       <c r="L134" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="N134" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="135" spans="2:14" x14ac:dyDescent="0.4">
@@ -3599,7 +3600,7 @@
         <v>235</v>
       </c>
       <c r="N135" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="136" spans="2:14" x14ac:dyDescent="0.4">
@@ -3619,7 +3620,7 @@
         <v>235</v>
       </c>
       <c r="N136" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="137" spans="2:14" x14ac:dyDescent="0.4">
@@ -3627,10 +3628,10 @@
         <v>233</v>
       </c>
       <c r="L137" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="N137" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="138" spans="2:14" x14ac:dyDescent="0.4">
@@ -3638,10 +3639,10 @@
         <v>234</v>
       </c>
       <c r="L138" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="N138" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
   </sheetData>
